--- a/data/trans_bre/P12_3_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P12_3_R-Provincia-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 5,59</t>
+          <t>-3,25; 5,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,92; 22,25</t>
+          <t>9,41; 22,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 12,27</t>
+          <t>0,43; 12,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,91</t>
+          <t>0,37; 2,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-40,22; 155,61</t>
+          <t>-45,38; 154,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,95; 262,52</t>
+          <t>63,25; 254,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 135,63</t>
+          <t>1,43; 141,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 9,61</t>
+          <t>1,9; 9,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 8,24</t>
+          <t>0,74; 8,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 6,74</t>
+          <t>0,37; 6,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 5,88</t>
+          <t>-0,86; 5,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,58; 156,52</t>
+          <t>17,91; 160,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,87; 154,27</t>
+          <t>7,26; 148,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,98; 218,22</t>
+          <t>4,64; 238,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-12,19; 138,27</t>
+          <t>-13,1; 152,13</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 2,61</t>
+          <t>-1,03; 2,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 10,04</t>
+          <t>1,28; 10,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 3,11</t>
+          <t>-3,49; 2,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 8,54</t>
+          <t>1,12; 8,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-84,61; —</t>
+          <t>-82,16; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,62; 247,87</t>
+          <t>15,26; 255,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-52,06; 95,44</t>
+          <t>-54,6; 89,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,14; 155,58</t>
+          <t>10,39; 168,34</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,53; 5,29</t>
+          <t>0,39; 5,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,64; 15,84</t>
+          <t>5,86; 16,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,02; 15,32</t>
+          <t>6,12; 15,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 8,55</t>
+          <t>-1,02; 8,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 1144,88</t>
+          <t>-2,7; 1259,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,1; 204,21</t>
+          <t>46,19; 217,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,21; 304,95</t>
+          <t>70,31; 297,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-15,29; 226,57</t>
+          <t>-13,88; 238,86</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 12,7</t>
+          <t>-0,12; 13,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,46; 14,07</t>
+          <t>3,01; 13,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,38; 16,32</t>
+          <t>1,59; 16,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 4,92</t>
+          <t>-5,98; 5,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 146,97</t>
+          <t>-4,23; 156,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,4; 508,8</t>
+          <t>39,32; 526,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,56; 146,52</t>
+          <t>7,14; 150,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-32,82; 39,15</t>
+          <t>-30,86; 45,25</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,08; 5,55</t>
+          <t>1,02; 5,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 7,26</t>
+          <t>-2,45; 7,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,49; 12,61</t>
+          <t>1,83; 12,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,4; 9,92</t>
+          <t>1,78; 9,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-29,55; 121,26</t>
+          <t>-25,82; 130,45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,0; 277,83</t>
+          <t>17,15; 286,82</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16,61; 174,94</t>
+          <t>15,61; 161,56</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 3,32</t>
+          <t>-1,62; 3,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 5,47</t>
+          <t>-0,22; 5,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 6,27</t>
+          <t>-0,49; 6,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 3,35</t>
+          <t>-12,65; 3,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-29,42; 108,73</t>
+          <t>-30,61; 109,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 125,0</t>
+          <t>-5,7; 115,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 102,73</t>
+          <t>-6,02; 101,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-58,6; 21,85</t>
+          <t>-60,49; 23,88</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,45; 8,56</t>
+          <t>2,74; 9,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 5,33</t>
+          <t>-1,37; 5,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 5,75</t>
+          <t>-0,02; 5,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,88; 18,6</t>
+          <t>3,98; 18,03</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>28,02; 149,74</t>
+          <t>33,72; 165,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 60,24</t>
+          <t>-10,94; 58,8</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 101,35</t>
+          <t>-0,59; 103,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>20,61; 315,88</t>
+          <t>21,36; 266,27</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,66</t>
+          <t>2,2; 4,7</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,7; 6,67</t>
+          <t>3,58; 6,77</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,98; 5,9</t>
+          <t>2,9; 5,75</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,71; 5,62</t>
+          <t>0,64; 5,47</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>37,51; 103,14</t>
+          <t>38,81; 104,09</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>42,33; 88,46</t>
+          <t>40,88; 90,04</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36,41; 85,18</t>
+          <t>35,64; 85,26</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,54; 69,49</t>
+          <t>7,71; 65,24</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P12_3_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P12_3_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>1,08</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 5,71</t>
+          <t>-2,74; 5,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,41; 22,94</t>
+          <t>8,94; 21,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 12,48</t>
+          <t>0,09; 12,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,07</t>
+          <t>0,46; 2,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-45,38; 154,83</t>
+          <t>-37,76; 138,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,25; 254,75</t>
+          <t>62,37; 254,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,43; 141,3</t>
+          <t>-3,0; 123,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,77</t>
+          <t>2,66</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>47,13%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,9; 9,93</t>
+          <t>2,07; 10,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 8,03</t>
+          <t>0,25; 7,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 6,63</t>
+          <t>0,54; 6,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 5,99</t>
+          <t>-0,69; 5,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,91; 160,83</t>
+          <t>19,83; 161,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,26; 148,86</t>
+          <t>-1,47; 146,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,64; 238,35</t>
+          <t>7,44; 217,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 152,13</t>
+          <t>-9,74; 140,92</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,86</t>
+          <t>4,75</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>63,79%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 2,55</t>
+          <t>-0,98; 2,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 10,19</t>
+          <t>1,19; 9,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 2,73</t>
+          <t>-3,68; 3,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,12; 8,63</t>
+          <t>0,69; 8,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-82,16; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,26; 255,1</t>
+          <t>11,66; 242,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-54,6; 89,45</t>
+          <t>-54,41; 104,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,39; 168,34</t>
+          <t>6,29; 142,97</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,18</t>
+          <t>6,23</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>108,06%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 5,24</t>
+          <t>0,6; 5,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,86; 16,64</t>
+          <t>6,04; 16,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,12; 15,21</t>
+          <t>5,88; 15,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 8,77</t>
+          <t>1,89; 10,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 1259,05</t>
+          <t>5,68; 1221,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,19; 217,82</t>
+          <t>45,49; 215,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,31; 297,71</t>
+          <t>61,17; 291,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-13,88; 238,86</t>
+          <t>17,67; 283,57</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,62</t>
+          <t>-0,78</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-3,87%</t>
+          <t>-4,84%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 13,15</t>
+          <t>-0,53; 13,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,01; 13,79</t>
+          <t>3,04; 14,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,59; 16,4</t>
+          <t>1,78; 16,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 5,44</t>
+          <t>-6,36; 4,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 156,16</t>
+          <t>-4,71; 158,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,32; 526,15</t>
+          <t>33,0; 590,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,14; 150,46</t>
+          <t>7,73; 145,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-30,86; 45,25</t>
+          <t>-33,42; 39,75</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5,72</t>
+          <t>5,69</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>75,2%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,02; 5,5</t>
+          <t>1,09; 5,76</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 7,24</t>
+          <t>-2,66; 7,42</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,83; 12,39</t>
+          <t>1,8; 12,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,78; 9,19</t>
+          <t>2,07; 9,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-25,82; 130,45</t>
+          <t>-24,25; 132,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,15; 286,82</t>
+          <t>18,08; 281,64</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15,61; 161,56</t>
+          <t>20,87; 172,24</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-2,53</t>
+          <t>3,75</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-15,59%</t>
+          <t>25,34%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 3,54</t>
+          <t>-1,57; 3,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 5,31</t>
+          <t>-0,3; 5,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 6,57</t>
+          <t>-0,38; 6,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,65; 3,56</t>
+          <t>-0,08; 7,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-30,61; 109,27</t>
+          <t>-28,83; 100,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 115,81</t>
+          <t>-6,65; 121,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 101,8</t>
+          <t>-5,98; 99,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-60,49; 23,88</t>
+          <t>-0,44; 59,8</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9,65</t>
+          <t>5,69</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>33,15%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,74; 9,16</t>
+          <t>2,9; 9,11</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 5,32</t>
+          <t>-1,36; 5,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 5,77</t>
+          <t>-0,3; 5,35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,98; 18,03</t>
+          <t>1,51; 9,09</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>33,72; 165,32</t>
+          <t>34,78; 159,57</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-10,94; 58,8</t>
+          <t>-11,57; 58,26</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 103,71</t>
+          <t>-5,43; 90,51</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>21,36; 266,27</t>
+          <t>7,58; 57,51</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3,25</t>
+          <t>4,08</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>38,68%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,7</t>
+          <t>2,29; 4,74</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,58; 6,77</t>
+          <t>3,67; 6,76</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,9; 5,75</t>
+          <t>2,86; 5,85</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,47</t>
+          <t>2,66; 5,56</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>38,81; 104,09</t>
+          <t>41,28; 107,41</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>40,88; 90,04</t>
+          <t>42,26; 92,4</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35,64; 85,26</t>
+          <t>34,84; 86,69</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7,71; 65,24</t>
+          <t>23,3; 57,53</t>
         </is>
       </c>
     </row>
